--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536131_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536131_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Á. MERLO</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.215</v>
+        <v>-0.5809</v>
       </c>
       <c r="E16" t="n">
-        <v>1.215</v>
+        <v>1.8534</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-2.4343</v>
       </c>
       <c r="G16" t="n">
-        <v>1.215</v>
+        <v>0.1047</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.0171</v>
       </c>
       <c r="I16" t="n">
-        <v>1.215</v>
+        <v>0.0876</v>
       </c>
       <c r="J16" t="n">
-        <v>1.215</v>
+        <v>1.1266</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.0456</v>
       </c>
       <c r="L16" t="n">
-        <v>1.215</v>
+        <v>0.081</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.0219</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.0285</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.0066</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.195</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.6549</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.4933</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.1617</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2256</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4457</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>A. DEL CERRO MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5809</v>
+        <v>-3.9351</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8534</v>
+        <v>-1.3011</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4343</v>
+        <v>-2.634</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1047</v>
+        <v>-5.4047</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0171</v>
+        <v>-3.1851</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0876</v>
+        <v>-2.2196</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1266</v>
+        <v>-1.262</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0456</v>
+        <v>-0.5165</v>
       </c>
       <c r="L17" t="n">
-        <v>0.081</v>
+        <v>-0.7455000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0219</v>
+        <v>-4.1427</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0285</v>
+        <v>-2.6686</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0066</v>
+        <v>-1.4741</v>
       </c>
       <c r="P17" t="n">
-        <v>0.195</v>
+        <v>1.7549</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.195</v>
+        <v>1.7549</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6549</v>
+        <v>-0.2852</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4933</v>
+        <v>-0.0391</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1617</v>
+        <v>-0.2461</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2256</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4457</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DEL CERRO MARTIN</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.9351</v>
+        <v>-4.2959</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3011</v>
+        <v>-1.8153</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.634</v>
+        <v>-2.4806</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.4047</v>
+        <v>-3.0672</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1851</v>
+        <v>-2.5797</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.2196</v>
+        <v>-0.4874</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.262</v>
+        <v>-0.894</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5165</v>
+        <v>-0.9345</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7455000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-4.1427</v>
+        <v>-2.1732</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.6686</v>
+        <v>-1.6453</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4741</v>
+        <v>-0.5279</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7549</v>
+        <v>0.585</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7549</v>
+        <v>1.5599</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2852</v>
+        <v>-0.8721</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0391</v>
+        <v>-0.2249</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2461</v>
+        <v>-0.6472</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9415</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2786</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>A. MERLO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.2959</v>
+        <v>-4.8621</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8153</v>
+        <v>-1.6642</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4806</v>
+        <v>-3.198</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.0672</v>
+        <v>-2.4052</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5797</v>
+        <v>-1.3588</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4874</v>
+        <v>-1.0465</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.894</v>
+        <v>1.6687</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9345</v>
+        <v>0.9722</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0.6965</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1732</v>
+        <v>-4.0739</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6453</v>
+        <v>-2.331</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5279</v>
+        <v>-1.743</v>
       </c>
       <c r="P19" t="n">
-        <v>0.585</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9749</v>
+        <v>-2.9248</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5599</v>
+        <v>1.3649</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8721</v>
+        <v>-0.897</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2249</v>
+        <v>-0.4081</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6472</v>
+        <v>-0.4889</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9415</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2786</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2201</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. MERLO</t>
+          <t>L. BRYAN JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.0771</v>
+        <v>-6.7829</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8792</v>
+        <v>-2.4575</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.198</v>
+        <v>-4.3254</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.6203</v>
+        <v>-5.4313</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3588</v>
+        <v>-3.0888</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.2615</v>
+        <v>-2.3425</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4537</v>
+        <v>-1.2919</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9722</v>
+        <v>-0.6924</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5185</v>
+        <v>-0.5995</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.0739</v>
+        <v>-4.1394</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.331</v>
+        <v>-2.3964</v>
       </c>
       <c r="O21" t="n">
         <v>-1.743</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5599</v>
+        <v>-0.195</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9248</v>
+        <v>-1.9499</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3649</v>
+        <v>1.7549</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.897</v>
+        <v>-0.5466</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4081</v>
+        <v>0.1742</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4889</v>
+        <v>-0.7208</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. BRYAN JR</t>
+          <t>U. RAZAQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7829</v>
+        <v>-7.4704</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4575</v>
+        <v>-5.364</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3254</v>
+        <v>-2.1064</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.4313</v>
+        <v>-7.4049</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0888</v>
+        <v>-5.4915</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3425</v>
+        <v>-1.9135</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2919</v>
+        <v>-3.6605</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6924</v>
+        <v>-2.275</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5995</v>
+        <v>-1.3855</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.1394</v>
+        <v>-3.7444</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.3964</v>
+        <v>-3.2165</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.743</v>
+        <v>-0.5279</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.195</v>
+        <v>-0.585</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.9499</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7549</v>
+        <v>1.3649</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5466</v>
+        <v>-1.3106</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1742</v>
+        <v>-1.2522</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7208</v>
+        <v>-0.0584</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.61</v>
+        <v>1.8301</v>
       </c>
       <c r="W22" t="n">
-        <v>0.61</v>
+        <v>1.4986</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2201</v>
+        <v>0.3315</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U. RAZAQUE</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4704</v>
+        <v>-10.6003</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.364</v>
+        <v>-8.5848</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1064</v>
+        <v>-2.0155</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.4049</v>
+        <v>-7.735</v>
       </c>
       <c r="H23" t="n">
-        <v>-5.4915</v>
+        <v>-5.3388</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9135</v>
+        <v>-2.3962</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.6605</v>
+        <v>-5.2191</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.275</v>
+        <v>-3.2181</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3855</v>
+        <v>-2.001</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.7444</v>
+        <v>-2.5159</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.2165</v>
+        <v>-2.1208</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5279</v>
+        <v>-0.3951</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.585</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9499</v>
+        <v>-2.9248</v>
       </c>
       <c r="R23" t="n">
         <v>1.3649</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3106</v>
+        <v>-0.8012</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2522</v>
+        <v>-0.4409</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0584</v>
+        <v>-0.3603</v>
       </c>
       <c r="V23" t="n">
-        <v>1.8301</v>
+        <v>-0.5042</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4986</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3315</v>
+        <v>-0.5042</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. MONES RIERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,152 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.6003</v>
+        <v>-41.1387</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.5848</v>
+        <v>-13.9674</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0155</v>
+        <v>-27.1714</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.735</v>
+        <v>-32.962</v>
       </c>
       <c r="H24" t="n">
-        <v>-5.3388</v>
+        <v>-22.853</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3962</v>
+        <v>-10.1091</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.2191</v>
+        <v>-4.4161</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.2181</v>
+        <v>-2.3087</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.001</v>
+        <v>-2.1074</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5159</v>
+        <v>-28.5458</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.1208</v>
+        <v>-20.5445</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3951</v>
+        <v>-8.0014</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5599</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9248</v>
+        <v>-11.6992</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3649</v>
+        <v>11.6992</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8012</v>
+        <v>-7.3409</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4409</v>
+        <v>-3.7937</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3603</v>
+        <v>-3.5473</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5042</v>
+        <v>-0.8356000000000001</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>5.9416</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5042</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536131_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>IREN BCBADAJOZ</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-41.1387</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-13.9674</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-27.1714</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-32.9621</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-22.853</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-10.1091</v>
-      </c>
-      <c r="J25" t="n">
-        <v>-4.4161</v>
-      </c>
-      <c r="K25" t="n">
-        <v>-2.3087</v>
-      </c>
-      <c r="L25" t="n">
-        <v>-2.1074</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-28.5458</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-20.5445</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-8.0014</v>
-      </c>
-      <c r="P25" t="n">
-        <v>-2.220446049250313e-16</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-11.6992</v>
-      </c>
-      <c r="R25" t="n">
-        <v>11.6992</v>
-      </c>
-      <c r="S25" t="n">
-        <v>-7.3409</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-3.7937</v>
-      </c>
-      <c r="U25" t="n">
-        <v>-3.5473</v>
-      </c>
-      <c r="V25" t="n">
-        <v>-0.8356000000000001</v>
-      </c>
-      <c r="W25" t="n">
-        <v>5.941599999999999</v>
-      </c>
-      <c r="X25" t="n">
-        <v>-6.777299999999999</v>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+        <v>-6.7773</v>
+      </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
